--- a/data-manipulation-scripts/sheets-cleanup/sheets/VARETA VALVULA 06_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/VARETA VALVULA 06_02.xlsx
@@ -28,7 +28,7 @@
     <t>7909201037538</t>
   </si>
   <si>
-    <t>VV GP TITAN CG125 1995 A 2008</t>
+    <t>VARETA VALVULA GP TITAN CG125 1995 A 2008</t>
   </si>
 </sst>
 </file>
